--- a/Doc/程式歷程.xlsx
+++ b/Doc/程式歷程.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgkamars\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Side_Project\GifComposerWpf\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B728A533-10CF-40FB-9672-78D5E89CFDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4FF9C0-6CB6-4484-8272-915A0F42A74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開發階段" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="81">
   <si>
     <t>版本</t>
   </si>
@@ -232,6 +232,90 @@
   </si>
   <si>
     <t>名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FluentIcons.Wpf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NuGet 套件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ButtonStyles.xaml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconBtnStyle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Style</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立含有 icon 與文字的按鈕樣式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconTextBtnStyle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立只有 icon 按鈕樣式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TextBlockStyles.xaml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>titleStyle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hintTextStyle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>labelStyle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>標題文字樣式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示文字樣式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>標籤文字樣式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainWindow.xaml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增圖片按鈕；刪除全部圖片按鈕；
+圖片列表；刪除圖片按鈕；上移按鈕；
+下移按鈕；拖曳圖片區塊；預覽圖片區塊；
+尺寸設定；循環次數設定；輸出路徑設定；
+產生 gif 按鈕；狀態列</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -658,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -753,6 +837,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1222,15 +1309,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="5" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="30.375" style="5" customWidth="1"/>
     <col min="4" max="4" width="9" style="5"/>
     <col min="5" max="5" width="36.125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="51.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="51.625" style="21" customWidth="1"/>
     <col min="7" max="7" width="32.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="26" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
@@ -1262,38 +1349,161 @@
         <v>24</v>
       </c>
     </row>
+    <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B2:B80">
+  <conditionalFormatting sqref="B2:B208">
     <cfRule type="expression" dxfId="13" priority="1">
-      <formula>$B$2="Other"</formula>
+      <formula>B2="Other"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="12" priority="2">
-      <formula>$B$2="Resource"</formula>
+      <formula>B2="Resource"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="4">
-      <formula>$B$2="Helper / Utility"</formula>
+      <formula>B2="Helper / Utility"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="5">
-      <formula>$B$2="Converter"</formula>
+      <formula>B2="Converter"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="6">
-      <formula>$B$2="Repository"</formula>
+      <formula>B2="Repository"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="7">
-      <formula>$B$2="Service"</formula>
+      <formula>B2="Service"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$B$2="Model"</formula>
+      <formula>B2="Model"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="9">
-      <formula>$B$2="ViewModel"</formula>
+      <formula>B2="ViewModel"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="10">
-      <formula>$B$2="View"</formula>
+      <formula>B2="View"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D80">
+  <conditionalFormatting sqref="D2:D208">
     <cfRule type="expression" dxfId="4" priority="11">
       <formula>D2="新增"</formula>
     </cfRule>
@@ -1319,13 +1529,13 @@
           <x14:formula1>
             <xm:f>選單!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D80</xm:sqref>
+          <xm:sqref>D2:D208</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F6C556B4-03A7-4A00-A5BF-2BB818AC178A}">
           <x14:formula1>
             <xm:f>選單!$D$2:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B80</xm:sqref>
+          <xm:sqref>B2:B208</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1335,20 +1545,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B193875-8373-4603-8186-2E01BA7DA4CE}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
+    <col min="1" max="1" width="37.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="23.375" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/程式歷程.xlsx
+++ b/Doc/程式歷程.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Side_Project\GifComposerWpf\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4FF9C0-6CB6-4484-8272-915A0F42A74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7382AE68-855B-4659-8AE9-6F06DA2C53B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
   <si>
     <t>版本</t>
   </si>
@@ -316,6 +316,74 @@
 下移按鈕；拖曳圖片區塊；預覽圖片區塊；
 尺寸設定；循環次數設定；輸出路徑設定；
 產生 gif 按鈕；狀態列</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommunityToolkit.Mvvm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IFileDialogService.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>載入圖片路徑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實作 IFileDialogService</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FileDialogService.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microsoft.Extensions.DependencyInjection</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>App.xaml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除 StartupUri="MainWindow.xaml"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>改用 DI 方式建立主視窗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 App.xaml.cs 建立 DI 容器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>App.xaml.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenFiles()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainViewModel.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增 LoadImages Command</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +667,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -738,11 +806,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -840,6 +932,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1309,14 +1413,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="5" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="5" customWidth="1"/>
     <col min="3" max="3" width="30.375" style="5" customWidth="1"/>
     <col min="4" max="4" width="9" style="5"/>
-    <col min="5" max="5" width="36.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="59.75" style="5" customWidth="1"/>
     <col min="6" max="6" width="51.625" style="21" customWidth="1"/>
     <col min="7" max="7" width="32.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="26" style="5" customWidth="1"/>
@@ -1350,6 +1454,9 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>81</v>
+      </c>
       <c r="B2" s="5" t="s">
         <v>54</v>
       </c>
@@ -1368,11 +1475,12 @@
       <c r="G2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="34" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="35"/>
       <c r="B3" s="5" t="s">
         <v>54</v>
       </c>
@@ -1391,8 +1499,10 @@
       <c r="G3" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="H3" s="35"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="35"/>
       <c r="B4" s="5" t="s">
         <v>54</v>
       </c>
@@ -1411,8 +1521,10 @@
       <c r="G4" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="H4" s="35"/>
     </row>
     <row r="5" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="35"/>
       <c r="B5" s="5" t="s">
         <v>54</v>
       </c>
@@ -1431,8 +1543,10 @@
       <c r="G5" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
       <c r="B6" s="5" t="s">
         <v>54</v>
       </c>
@@ -1451,8 +1565,10 @@
       <c r="G6" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
       <c r="B7" s="5" t="s">
         <v>36</v>
       </c>
@@ -1471,8 +1587,105 @@
       <c r="G7" s="5" t="s">
         <v>79</v>
       </c>
+      <c r="H7" s="36"/>
+    </row>
+    <row r="8" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="35"/>
+      <c r="B9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="35"/>
+    </row>
+    <row r="10" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="35"/>
+      <c r="B10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="35"/>
+    </row>
+    <row r="11" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="35"/>
+      <c r="B11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="35"/>
+    </row>
+    <row r="12" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="36"/>
+      <c r="B12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="36"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="H8:H12"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B2:B208">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -1545,16 +1758,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B193875-8373-4603-8186-2E01BA7DA4CE}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="67.375" style="5" customWidth="1"/>
     <col min="2" max="2" width="23.375" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="32" t="s">
@@ -1562,12 +1775,34 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>62</v>
       </c>
+    </row>
+    <row r="3" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+    </row>
+    <row r="7" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Doc/程式歷程.xlsx
+++ b/Doc/程式歷程.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Side_Project\GifComposerWpf\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7382AE68-855B-4659-8AE9-6F06DA2C53B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B996F98D-E89A-4AC6-9BB4-BC99867464B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="選單" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">開發階段!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">開發階段!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="135">
   <si>
     <t>版本</t>
   </si>
@@ -386,12 +386,153 @@
     <t>新增 LoadImages Command</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>User Control</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImageItemView.xaml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImageItemViewModel.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">圖片項目 ViewModel </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImageModel.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖片資訊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IImageService</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImageService</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetImageInfo()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實作 GetImageInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取得圖片資訊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖片項目 UI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立屬性：Order、Name、Path、Width、Height、Thumbnail</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立資料綁定的屬性。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Record</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>註冊 IImageService 與 ImageService</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>告訴 DI Container：
+當有人需要 IImageService 時，請提供 ImageService，
+而且整個程式只共用同一個 ImageService 實例。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interface</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部刪除按鈕功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearAllImages()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>做出可以點選 ImageItemView  的效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>將 ItemsControl 改成 ListBox</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gong-wpf-dragdrop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Behaviors</t>
+  </si>
+  <si>
+    <t>Behaviors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImageItemDropHandler.cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖片列表中項目拖曳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實作 IDropTarget</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.10</t>
+  </si>
+  <si>
+    <t>2026.08.11</t>
+  </si>
+  <si>
+    <t>2026.08.12</t>
+  </si>
+  <si>
+    <t>2026.08.13</t>
+  </si>
+  <si>
+    <t>2026.08.14</t>
+  </si>
+  <si>
+    <t>2026.08.15</t>
+  </si>
+  <si>
+    <t>2026.08.16</t>
+  </si>
+  <si>
+    <t>2026.08.17</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,8 +703,16 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0C343D"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -663,6 +812,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -834,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -933,6 +1088,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -942,14 +1100,396 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0C343D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0C343D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF5F497A"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4DFEC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF38761D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC55A11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF741B47"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAD1DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F7F7F"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB45F06"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF0E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F7F7F"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0C343D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF5F497A"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4DFEC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF38761D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC55A11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF741B47"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAD1DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F7F7F"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB45F06"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF0E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F7F7F"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1127,6 +1667,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0C343D"/>
+      <color rgb="FFD0E0E3"/>
       <color rgb="FF7F7F7F"/>
       <color rgb="FFF2F2F2"/>
       <color rgb="FFB45F06"/>
@@ -1135,8 +1677,6 @@
       <color rgb="FF741B47"/>
       <color rgb="FFE2EFDA"/>
       <color rgb="FF375623"/>
-      <color rgb="FFFCE4D6"/>
-      <color rgb="FFC55A11"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1413,15 +1953,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="5" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="30.375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="5" customWidth="1"/>
     <col min="4" max="4" width="9" style="5"/>
-    <col min="5" max="5" width="59.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="51.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="50.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="67.625" style="21" customWidth="1"/>
     <col min="7" max="7" width="32.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="26" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
@@ -1454,7 +1994,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="35" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1475,12 +2015,12 @@
       <c r="G2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="35" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35"/>
+      <c r="A3" s="36"/>
       <c r="B3" s="5" t="s">
         <v>54</v>
       </c>
@@ -1499,10 +2039,10 @@
       <c r="G3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="35"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="5" t="s">
         <v>54</v>
       </c>
@@ -1521,10 +2061,10 @@
       <c r="G4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="35"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="5" t="s">
         <v>54</v>
       </c>
@@ -1543,10 +2083,10 @@
       <c r="G5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="5" t="s">
         <v>54</v>
       </c>
@@ -1565,10 +2105,10 @@
       <c r="G6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" spans="1:8" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="5" t="s">
         <v>36</v>
       </c>
@@ -1587,10 +2127,10 @@
       <c r="G7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="35" t="s">
         <v>95</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1608,12 +2148,15 @@
       <c r="F8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="G8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H8" s="35" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="5" t="s">
         <v>45</v>
       </c>
@@ -1626,10 +2169,10 @@
       <c r="E9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="5" t="s">
         <v>58</v>
       </c>
@@ -1645,10 +2188,10 @@
       <c r="F10" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="5" t="s">
         <v>58</v>
       </c>
@@ -1661,10 +2204,10 @@
       <c r="E11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
@@ -1677,67 +2220,272 @@
       <c r="E12" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="37"/>
+    </row>
+    <row r="13" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="35">
+        <v>0.02</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="36"/>
+      <c r="B14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36"/>
+      <c r="B15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="36"/>
+      <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="36"/>
+      <c r="B17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="36"/>
+      <c r="B18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="36"/>
+      <c r="B19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36"/>
+      <c r="B20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="37"/>
+      <c r="B21" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="H2:H7"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="H8:H12"/>
+    <mergeCell ref="A13:A21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B2:B208">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>B2="Other"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="14" priority="4">
       <formula>B2="Resource"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="4">
+    <cfRule type="expression" dxfId="13" priority="6">
       <formula>B2="Helper / Utility"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>B2="Converter"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>B2="Repository"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>B2="Service"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>B2="Model"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>B2="ViewModel"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>B2="View"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D208">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>D2="新增"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="12">
+    <cfRule type="expression" dxfId="5" priority="14">
       <formula>D2="修改"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="13">
+    <cfRule type="expression" dxfId="4" priority="15">
       <formula>D2="修復"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="14">
+    <cfRule type="expression" dxfId="3" priority="16">
       <formula>D2="重構"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="2" priority="18">
       <formula>D2="刪除"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$B2="Behaviors"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:B30">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$B21="Behaviors"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{94CD53A7-2256-444E-8A65-C007F1459AF0}">
           <x14:formula1>
             <xm:f>選單!$A$2:$A$6</xm:f>
@@ -1748,7 +2496,13 @@
           <x14:formula1>
             <xm:f>選單!$D$2:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B208</xm:sqref>
+          <xm:sqref>B115:B208 B2:B20</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{67C3F24B-2241-4D56-BBCD-2A9FA4925393}">
+          <x14:formula1>
+            <xm:f>選單!$D$2:$D$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>B21:B114</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1767,7 +2521,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="32" t="s">
@@ -1799,7 +2553,12 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21"/>
+      <c r="A5" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21"/>
@@ -1900,7 +2659,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523A98AE-9B03-4622-BFA0-C0A6F1497B92}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -2058,6 +2817,11 @@
         <v>59</v>
       </c>
     </row>
+    <row r="11" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="38" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Doc/程式歷程.xlsx
+++ b/Doc/程式歷程.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Side_Project\GifComposerWpf\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B996F98D-E89A-4AC6-9BB4-BC99867464B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D2EC09-76BC-4B97-8B21-B0DDF017277C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="136">
   <si>
     <t>版本</t>
   </si>
@@ -507,25 +507,39 @@
     <t>2026.08.10</t>
   </si>
   <si>
+    <t>清除全部圖片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立 ClearAllImages()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立 Delay 屬性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立 isLockDelayInput 屬性。
+建立 lockDelayInput()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制啟用延遲時間輸入框。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>2026.08.11</t>
-  </si>
-  <si>
-    <t>2026.08.12</t>
-  </si>
-  <si>
-    <t>2026.08.13</t>
-  </si>
-  <si>
-    <t>2026.08.14</t>
-  </si>
-  <si>
-    <t>2026.08.15</t>
-  </si>
-  <si>
-    <t>2026.08.16</t>
-  </si>
-  <si>
-    <t>2026.08.17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 建立 SelectedImage 屬性
+2. 建立 RemoveSelectedImage()
+3. 建立 CanRemoveSelectedImage()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刪除選取的圖片，並控制啟用刪除按鈕。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1091,6 +1105,9 @@
     <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1098,40 +1115,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0C343D"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0E0E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0C343D"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0E0E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <b/>
@@ -1201,107 +1191,11 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FF1F4E78"/>
+        <color rgb="FF0C343D"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF38761D"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC55A11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF741B47"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEAD1DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F7F7F"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB45F06"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF0E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F7F7F"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFD0E0E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1314,244 +1208,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFD0E0E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF5F497A"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4DFEC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF1F4E78"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF1F4E78"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF38761D"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC55A11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF741B47"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEAD1DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F7F7F"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB45F06"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF0E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F7F7F"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF5F497A"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4DFEC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF1F4E78"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1953,14 +1609,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="5" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="5" customWidth="1"/>
     <col min="3" max="3" width="42.125" style="5" customWidth="1"/>
     <col min="4" max="4" width="9" style="5"/>
-    <col min="5" max="5" width="50.375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="50.375" style="21" customWidth="1"/>
     <col min="6" max="6" width="67.625" style="21" customWidth="1"/>
     <col min="7" max="7" width="32.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="26" style="5" customWidth="1"/>
@@ -1994,7 +1650,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="36" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2006,7 +1662,7 @@
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="21" t="s">
         <v>68</v>
       </c>
       <c r="F2" s="21" t="s">
@@ -2015,12 +1671,12 @@
       <c r="G2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="36" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="5" t="s">
         <v>54</v>
       </c>
@@ -2030,7 +1686,7 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="21" t="s">
         <v>64</v>
       </c>
       <c r="F3" s="21" t="s">
@@ -2039,10 +1695,10 @@
       <c r="G3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="36"/>
+      <c r="H3" s="37"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="5" t="s">
         <v>54</v>
       </c>
@@ -2052,7 +1708,7 @@
       <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="21" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="21" t="s">
@@ -2061,10 +1717,10 @@
       <c r="G4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="36"/>
+      <c r="H4" s="37"/>
     </row>
     <row r="5" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="5" t="s">
         <v>54</v>
       </c>
@@ -2074,7 +1730,7 @@
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="21" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="21" t="s">
@@ -2083,10 +1739,10 @@
       <c r="G5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="5" t="s">
         <v>54</v>
       </c>
@@ -2096,7 +1752,7 @@
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="21" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -2105,10 +1761,10 @@
       <c r="G6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="37"/>
     </row>
     <row r="7" spans="1:8" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="5" t="s">
         <v>36</v>
       </c>
@@ -2118,7 +1774,7 @@
       <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="21" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="33" t="s">
@@ -2127,10 +1783,10 @@
       <c r="G7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>95</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -2142,7 +1798,7 @@
       <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="21" t="s">
         <v>94</v>
       </c>
       <c r="F8" s="21" t="s">
@@ -2151,12 +1807,12 @@
       <c r="G8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="36" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="5" t="s">
         <v>45</v>
       </c>
@@ -2166,13 +1822,13 @@
       <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="37"/>
     </row>
     <row r="10" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="5" t="s">
         <v>58</v>
       </c>
@@ -2182,16 +1838,16 @@
       <c r="D10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="21" t="s">
         <v>90</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="37"/>
     </row>
     <row r="11" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="5" t="s">
         <v>58</v>
       </c>
@@ -2201,13 +1857,13 @@
       <c r="D11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
@@ -2217,13 +1873,13 @@
       <c r="D12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="H12" s="37"/>
+      <c r="H12" s="38"/>
     </row>
     <row r="13" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35">
+      <c r="A13" s="36">
         <v>0.02</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -2235,7 +1891,7 @@
       <c r="D13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="21" t="s">
         <v>110</v>
       </c>
       <c r="G13" s="5" t="s">
@@ -2246,7 +1902,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="5" t="s">
         <v>39</v>
       </c>
@@ -2256,18 +1912,18 @@
       <c r="D14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="21" t="s">
         <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="36" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="5" t="s">
         <v>42</v>
       </c>
@@ -2277,7 +1933,7 @@
       <c r="D15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="21" t="s">
         <v>104</v>
       </c>
       <c r="F15" s="33" t="s">
@@ -2286,12 +1942,10 @@
       <c r="G15" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>128</v>
-      </c>
+      <c r="H15" s="37"/>
     </row>
     <row r="16" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
@@ -2301,7 +1955,7 @@
       <c r="D16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="21" t="s">
         <v>107</v>
       </c>
       <c r="F16" s="21" t="s">
@@ -2310,12 +1964,10 @@
       <c r="G16" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>129</v>
-      </c>
+      <c r="H16" s="37"/>
     </row>
     <row r="17" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="5" t="s">
         <v>45</v>
       </c>
@@ -2325,15 +1977,13 @@
       <c r="D17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>130</v>
-      </c>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="5" t="s">
         <v>58</v>
       </c>
@@ -2343,18 +1993,16 @@
       <c r="D18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="21" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>131</v>
-      </c>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="5" t="s">
         <v>39</v>
       </c>
@@ -2364,18 +2012,16 @@
       <c r="D19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="21" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>132</v>
-      </c>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="5" t="s">
         <v>36</v>
       </c>
@@ -2385,18 +2031,16 @@
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="21" t="s">
         <v>119</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="5" t="s">
         <v>122</v>
       </c>
@@ -2406,18 +2050,96 @@
       <c r="D21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="21" t="s">
         <v>126</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="36">
+        <v>0.03</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="37"/>
+      <c r="B23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="37"/>
+    </row>
+    <row r="24" spans="1:8" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="37"/>
+      <c r="B24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="37"/>
+    </row>
+    <row r="25" spans="1:8" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="38"/>
+      <c r="B25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="33" t="s">
         <v>134</v>
       </c>
+      <c r="F25" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="H14:H21"/>
+    <mergeCell ref="H22:H25"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="H2:H7"/>
     <mergeCell ref="A8:A12"/>
@@ -2454,31 +2176,31 @@
       <formula>B2="View"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D208">
-    <cfRule type="expression" dxfId="6" priority="13">
-      <formula>D2="新增"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="14">
-      <formula>D2="修改"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="15">
-      <formula>D2="修復"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="16">
-      <formula>D2="重構"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
-      <formula>D2="刪除"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$B2="Behaviors"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:B30">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$B21="Behaviors"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D208">
+    <cfRule type="expression" dxfId="4" priority="13">
+      <formula>D2="新增"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="14">
+      <formula>D2="修改"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="15">
+      <formula>D2="修復"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="16">
+      <formula>D2="重構"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>D2="刪除"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2818,7 +2540,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="35" t="s">
         <v>123</v>
       </c>
     </row>
